--- a/output/pdf_financials_xlsx/MINK.xlsx
+++ b/output/pdf_financials_xlsx/MINK.xlsx
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.010815</v>
+        <v>0.115101</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.049104</v>
+        <v>0.43928</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.119837</v>
+        <v>1.338034</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.088287</v>
+        <v>0.655108</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.105559</v>
+        <v>0.649976</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.010815</v>
+        <v>-0.115101</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.049104</v>
+        <v>-0.43928</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.119837</v>
+        <v>-1.338034</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.088287</v>
+        <v>-0.655108</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.105559</v>
+        <v>-0.649976</v>
       </c>
     </row>
     <row r="12">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.518119</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.170629</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.518119</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.170629</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.518119</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">

--- a/output/pdf_financials_xlsx/MINK.xlsx
+++ b/output/pdf_financials_xlsx/MINK.xlsx
@@ -2814,16 +2814,16 @@
         <v>0.068</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.058031</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.045732</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.028637</v>
       </c>
     </row>
     <row r="108">
@@ -4344,7 +4344,11 @@
           <t>Share-based payments, note 7 124,435</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -5549,7 +5553,11 @@
           <t>Share-based payments, note 7 28,637</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -6661,7 +6669,11 @@
           <t>Share-based payments, note 7 45,732</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -7624,7 +7636,11 @@
           <t>Share-based payments, note 7 58,031</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -9238,7 +9254,11 @@
           <t>Professional fees, note 8</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MINK.xlsx
+++ b/output/pdf_financials_xlsx/MINK.xlsx
@@ -3467,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I174"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4165,24 +4165,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Net loss for the year (569,381)</t>
+          <t>As at, December</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E19" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4199,31 +4193,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>-0.501833</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Interest income -</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.010125</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4240,31 +4238,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>-0.001833</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation expenses, note 6 and note 7 41,250</t>
+          <t>Issued capital, note 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="5" t="n">
+        <v>0.513792</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4290,24 +4288,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Flow-through share premium income, note 6 and note 10 (23,343)</t>
+          <t>Equity reserves, note 6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>0.110405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4324,35 +4320,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>-0.029473</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 124,435</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Nature of operations and going concern, note</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4369,8 +4361,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0.028637</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -4381,12 +4375,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation total</t>
+          <t>Net loss for the year (569,381)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -4395,8 +4389,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>-0.047101</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4409,7 +4405,7 @@
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-0.504502</v>
+        <v>-0.501833</v>
       </c>
     </row>
     <row r="25">
@@ -4420,19 +4416,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Amounts receivable 19,010</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Interest income -</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4454,7 +4446,7 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.029063</v>
+        <v>-0.001833</v>
       </c>
     </row>
     <row r="26">
@@ -4465,12 +4457,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Harmonized Sales Tax receivable (3,156)</t>
+          <t>Shares issued for exploration and evaluation expenses, note 6 and note 7 41,250</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -4494,8 +4486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0.024844</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4506,12 +4500,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaid expenses (74,454)</t>
+          <t>Flow-through share premium income, note 6 and note 10 (23,343)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -4536,7 +4530,7 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.007866</v>
+        <v>-0.029473</v>
       </c>
     </row>
     <row r="28">
@@ -4547,17 +4541,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (24,926)</t>
+          <t>Share-based payments, note 7 124,435</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4581,7 +4575,7 @@
         </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.015407</v>
+        <v>0.028637</v>
       </c>
     </row>
     <row r="29">
@@ -4592,12 +4586,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital (83,526)</t>
+          <t>Shares issued for exploration and evaluation total</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -4606,10 +4600,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="5" t="n">
+        <v>-0.047101</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4622,7 +4614,7 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.07718</v>
+        <v>-0.504502</v>
       </c>
     </row>
     <row r="30">
@@ -4638,12 +4630,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (510,565)</t>
+          <t>Amounts receivable 19,010</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4667,7 +4659,7 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.427322</v>
+        <v>0.029063</v>
       </c>
     </row>
     <row r="31">
@@ -4678,12 +4670,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Recovery (increase) of restricted cash, note 10 26,155</t>
+          <t>Harmonized Sales Tax receivable (3,156)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -4708,7 +4700,7 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.05</v>
+        <v>0.024844</v>
       </c>
     </row>
     <row r="32">
@@ -4719,19 +4711,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net cash provided by investing activities 26,155</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Prepaid expenses (74,454)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -4753,7 +4741,7 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.05</v>
+        <v>0.007866</v>
       </c>
     </row>
     <row r="33">
@@ -4764,15 +4752,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Non-brokered private placement, note 6 792,540</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (24,926)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4794,7 +4786,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.268395</v>
+        <v>0.015407</v>
       </c>
     </row>
     <row r="34">
@@ -4805,12 +4797,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Flow-through shares, note 6 322,378</t>
+          <t>Net change in non-cash working capital (83,526)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -4835,7 +4827,7 @@
         </is>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.16884</v>
+        <v>0.07718</v>
       </c>
     </row>
     <row r="35">
@@ -4846,15 +4838,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Issue costs, note 6 (112,118)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Net cash used in operating activities (510,565)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4876,7 +4872,7 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.042571</v>
+        <v>-0.427322</v>
       </c>
     </row>
     <row r="36">
@@ -4887,12 +4883,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warrants exercised, note 6 and note 7 -</t>
+          <t>Recovery (increase) of restricted cash, note 10 26,155</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4917,7 +4913,7 @@
         </is>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.010755</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="37">
@@ -4928,17 +4924,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 1,002,800</t>
+          <t>Net cash provided by investing activities 26,155</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4962,7 +4958,7 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.405419</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="38">
@@ -4978,12 +4974,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents 518,390</t>
+          <t>Non-brokered private placement, note 6 792,540</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5007,7 +5003,7 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>-0.07190199999999999</v>
+        <v>0.268395</v>
       </c>
     </row>
     <row r="39">
@@ -5023,14 +5019,10 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year 176,745</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Flow-through shares, note 6 322,378</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -5052,7 +5044,7 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.248647</v>
+        <v>0.16884</v>
       </c>
     </row>
     <row r="40">
@@ -5068,14 +5060,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year 695,135</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Issue costs, note 6 (112,118)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5097,7 +5085,7 @@
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.176745</v>
+        <v>-0.042571</v>
       </c>
     </row>
     <row r="41">
@@ -5108,12 +5096,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1. Nature of operations and going concern</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MINK Ventures Corporation (the "Company" or "MINK") was incorporated on March 9,</t>
+          <t>Warrants exercised, note 6 and note 7 -</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -5122,17 +5110,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.002021</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.010755</v>
       </c>
     </row>
     <row r="42">
@@ -5143,15 +5137,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(b)  Basis of preparation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>April 28,</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Net cash provided by financing activities 1,002,800</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -5173,7 +5171,7 @@
         </is>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.002026</v>
+        <v>0.405419</v>
       </c>
     </row>
     <row r="43">
@@ -5184,15 +5182,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Company's financial statements.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Classification of Liabilities as Current or Non-current (Amendments to IAS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Change in cash and cash equivalents 518,390</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5208,11 +5210,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>1e-06</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>1e-06</v>
+        <v>-0.07190199999999999</v>
       </c>
     </row>
     <row r="44">
@@ -5223,15 +5227,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Classification and Measurement of Financial Instruments (Amendments to IFRS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year 176,745</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5247,11 +5255,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>9e-06</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="5" t="n">
-        <v>9e-06</v>
+        <v>0.248647</v>
       </c>
     </row>
     <row r="45">
@@ -5262,15 +5272,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>and IFRS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year 695,135</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5286,11 +5300,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>7e-06</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="5" t="n">
-        <v>7e-06</v>
+        <v>0.176745</v>
       </c>
     </row>
     <row r="46">
@@ -5301,12 +5317,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>1. Nature of operations and going concern</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>In May 2024, the IASB issued amendments to IFRS 9 Financial Instruments and IFRS</t>
+          <t>MINK Ventures Corporation (the "Company" or "MINK") was incorporated on March 9,</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5315,21 +5331,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.002021</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>7e-06</v>
+        <v>0.002021</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>7e-06</v>
+        <v>0.002021</v>
       </c>
     </row>
     <row r="47">
@@ -5340,12 +5352,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>(b)  Basis of preparation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The amendments are effective for annual periods starting on or after January 1,</t>
+          <t>April 28,</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5364,8 +5376,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>0.002026</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I47" s="5" t="n">
         <v>0.002026</v>
@@ -5379,12 +5393,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Company's financial statements.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net loss for the year (501,833)</t>
+          <t>Classification of Liabilities as Current or Non-current (Amendments to IAS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5404,12 +5418,10 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-1.152554</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-06</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>1e-06</v>
       </c>
     </row>
     <row r="49">
@@ -5420,12 +5432,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Interest income (1,833)</t>
+          <t>Classification and Measurement of Financial Instruments (Amendments to IFRS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -5444,15 +5456,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>9e-06</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>9e-06</v>
       </c>
     </row>
     <row r="50">
@@ -5463,12 +5471,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and evaluation expenses, note 6 and note 7 -</t>
+          <t>and IFRS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -5488,12 +5496,10 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.22694</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7e-06</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>7e-06</v>
       </c>
     </row>
     <row r="51">
@@ -5504,12 +5510,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Flow-through share premium income, note 6 and note 10 (29,473)</t>
+          <t>In May 2024, the IASB issued amendments to IFRS 9 Financial Instruments and IFRS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5529,12 +5535,10 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-0.103681</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7e-06</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>7e-06</v>
       </c>
     </row>
     <row r="52">
@@ -5545,19 +5549,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 28,637</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>The amendments are effective for annual periods starting on or after January 1,</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -5574,12 +5574,10 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.045732</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002026</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.002026</v>
       </c>
     </row>
     <row r="53">
@@ -5590,12 +5588,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and total</t>
+          <t>Net loss for the year (501,833)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -5609,11 +5607,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.301249</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.983563</v>
+        <v>-1.152554</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5629,19 +5629,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Amounts receivable 29,062</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Interest income (1,833)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5657,8 +5653,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="5" t="n">
-        <v>-0.07217899999999999</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5674,12 +5672,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Harmonized Sales Tax receivable 24,844</t>
+          <t>Shares and warrants issued for exploration and evaluation expenses, note 6 and note 7 -</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -5699,7 +5697,7 @@
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>-0.018906</v>
+        <v>0.22694</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5715,19 +5713,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prepaid expenses 7,866</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Flow-through share premium income, note 6 and note 10 (29,473)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5744,7 +5738,7 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.011478</v>
+        <v>-0.103681</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5760,17 +5754,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 15,409</t>
+          <t>Share-based payments, note 7 28,637</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5789,7 +5783,7 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>-0.156548</v>
+        <v>0.045732</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5805,19 +5799,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cash provided in non-cash working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital 77,181</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Shares and warrants issued for exploration and total</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5828,13 +5818,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G58" s="5" t="n">
+        <v>-0.301249</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-0.259111</v>
+        <v>-0.983563</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5855,12 +5843,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (427,321)</t>
+          <t>Amounts receivable 29,062</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5879,7 +5867,7 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>-1.242674</v>
+        <v>-0.07217899999999999</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5895,12 +5883,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Purchase of restricted cash equivalent (50,000)</t>
+          <t>Harmonized Sales Tax receivable 24,844</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -5919,10 +5907,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H60" s="5" t="n">
+        <v>-0.018906</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5938,17 +5924,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Net cash provided by investing activities (50,000)</t>
+          <t>Prepaid expenses 7,866</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5966,10 +5952,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H61" s="5" t="n">
+        <v>-0.011478</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5985,15 +5969,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Non-brokered private placement, note 6 268,395</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 15,409</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -6010,7 +5998,7 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.2768</v>
+        <v>-0.156548</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6026,15 +6014,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Flow-through shares, note 6 168,840</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Net change in non-cash working capital 77,181</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6051,7 +6043,7 @@
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.10986</v>
+        <v>-0.259111</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6067,15 +6059,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash provided in non-cash working capital items</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Issue costs, note 6 (42,571)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net cash used in operating activities (427,321)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -6092,7 +6088,7 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>-0.07037599999999999</v>
+        <v>-1.242674</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6108,12 +6104,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Warrants exercised,note 6 and note 7 10,755</t>
+          <t>Purchase of restricted cash equivalent (50,000)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -6132,8 +6128,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>0.004406</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6149,17 +6147,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 405,419</t>
+          <t>Net cash provided by investing activities (50,000)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6177,8 +6175,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
-        <v>0.32069</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents (71,902)</t>
+          <t>Non-brokered private placement, note 6 268,395</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>-0.921982</v>
+        <v>0.2768</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6244,14 +6244,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year 248,647</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Flow-through shares, note 6 168,840</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6268,7 +6264,7 @@
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>1.170629</v>
+        <v>0.10986</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6289,14 +6285,10 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cash and cash equivalnets, end of year 176,745</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Issue costs, note 6 (42,571)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6313,7 +6305,7 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.248647</v>
+        <v>-0.07037599999999999</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6334,7 +6326,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash 176,745</t>
+          <t>Warrants exercised,note 6 and note 7 10,755</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6354,7 +6346,7 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.196539</v>
+        <v>0.004406</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6375,10 +6367,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cash equivalents -</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Net cash provided by financing activities 405,419</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -6395,7 +6391,7 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.052108</v>
+        <v>0.32069</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6416,12 +6412,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
+          <t>Change in cash and cash equivalents (71,902)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6434,11 +6430,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n">
-        <v>1.170629</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.248647</v>
+        <v>-0.921982</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6454,15 +6452,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supplemental information,</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Finders' warrants issued, note 6 and note 7 -</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year 248,647</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6479,7 +6481,7 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.005624</v>
+        <v>1.170629</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6495,15 +6497,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(b)  Basis of preparation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>April 23,</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Cash and cash equivalnets, end of year 176,745</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -6520,7 +6526,7 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.002025</v>
+        <v>0.248647</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6536,12 +6542,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net loss for the year (1,152,554)</t>
+          <t>Cash 176,745</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -6555,13 +6561,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G75" s="5" t="n">
-        <v>-0.43928</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.196539</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6577,12 +6583,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and evaluation expenses, note 6 and note 7 226,940</t>
+          <t>Cash equivalents -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6596,13 +6602,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.052108</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6618,15 +6624,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flow-through share premium income, note 6 and note 10 (103,681)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6637,15 +6647,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" s="5" t="n">
+        <v>1.170629</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.248647</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6661,19 +6667,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for exploration and</t>
+          <t>Supplemental information,</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 45,732</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Finders' warrants issued, note 6 and note 7 -</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -6684,13 +6686,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" s="5" t="n">
-        <v>0.058031</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0.005624</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6706,12 +6708,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>working capital items</t>
+          <t>(b)  Basis of preparation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Amounts receivable (91,084)</t>
+          <t>April 23,</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6725,13 +6727,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" s="5" t="n">
-        <v>-0.014219</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.002025</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6747,12 +6749,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prepaid expenses (11,478)</t>
+          <t>Net loss for the year (1,152,554)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6766,10 +6768,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" s="5" t="n">
+        <v>-0.43928</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6790,19 +6790,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (156,547)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Shares and warrants issued for exploration and evaluation expenses, note 6 and note 7 226,940</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -6814,7 +6810,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.193983</v>
+        <v>0.08</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6835,12 +6831,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital (259,109)</t>
+          <t>Flow-through share premium income, note 6 and note 10 (103,681)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6854,8 +6850,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G82" s="5" t="n">
-        <v>0.179764</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6876,15 +6874,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>working capital items</t>
+          <t>Shares and warrants issued for exploration and</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net cash (used in) operating activities (1,242,672)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Share-based payments, note 7 45,732</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -6896,7 +6898,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.121485</v>
+        <v>0.058031</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6917,12 +6919,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>working capital items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Non-brokered private placement, note 6 276,800</t>
+          <t>Amounts receivable (91,084)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6937,7 +6939,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.40811</v>
+        <v>-0.014219</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6958,12 +6960,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>working capital items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Flow-through shares, note 6 109,860</t>
+          <t>Prepaid expenses (11,478)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6977,8 +6979,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G85" s="5" t="n">
-        <v>0.483767</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6999,15 +7003,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>working capital items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Issue costs, note 6 (70,376)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (156,547)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7019,7 +7027,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.117882</v>
+        <v>0.193983</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -7040,12 +7048,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>working capital items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Warrants exercised,note 6 and note 7 4,406</t>
+          <t>Net change in non-cash working capital (259,109)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7059,10 +7067,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G87" s="5" t="n">
+        <v>0.179764</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -7083,19 +7089,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>working capital items</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 320,690</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Net cash (used in) operating activities (1,242,672)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7107,7 +7109,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.773995</v>
+        <v>-0.121485</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7133,10 +7135,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents (921,982)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Non-brokered private placement, note 6 276,800</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -7148,7 +7154,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.65251</v>
+        <v>0.40811</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7174,14 +7180,10 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year 1,170,629</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Flow-through shares, note 6 109,860</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7193,7 +7195,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.518119</v>
+        <v>0.483767</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7219,14 +7221,10 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cash and cash equivalnets, end of year 248,647</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Issue costs, note 6 (70,376)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -7238,7 +7236,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1.170629</v>
+        <v>-0.117882</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7264,7 +7262,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cash 196,539</t>
+          <t>Warrants exercised,note 6 and note 7 4,406</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7278,8 +7276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" s="5" t="n">
-        <v>1.170629</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -7305,10 +7305,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cash equivalents 52,108</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Net cash provided by financing activities 320,690</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -7319,10 +7323,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>0.773995</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -7343,12 +7345,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supplemental information,</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Finders' warrants issued, note 6 and note 7 5,624</t>
+          <t>Change in cash and cash equivalents (921,982)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7363,7 +7365,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.014298</v>
+        <v>0.65251</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -7384,15 +7386,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>(b)  Basis of preparation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>April 25,</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year 1,170,629</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -7404,7 +7410,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.518119</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7425,15 +7431,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Classification of Liabilities as Current or Non-current (Amendments to IAS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Cash and cash equivalnets, end of year 248,647</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -7445,7 +7455,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1e-06</v>
+        <v>1.170629</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7466,12 +7476,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>financial statements.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>exercise of a conversion option meeting the definition of an equity instrument. The amendments are effective for annual periods beginning on January 1,</t>
+          <t>Cash 196,539</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7486,7 +7496,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.002024</v>
+        <v>1.170629</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7505,10 +7515,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>For the period of incorporation from March 9 to December 31</t>
+          <t>Cash equivalents 52,108</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7517,8 +7531,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>0.002021</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -7544,12 +7560,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Supplemental information,</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Net loss for the year (439,280)</t>
+          <t>Finders' warrants issued, note 6 and note 7 5,624</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7558,13 +7574,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>-0.115101</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.014298</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7585,12 +7601,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>(b)  Basis of preparation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation expenses 80,000</t>
+          <t>April 25,</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7604,10 +7620,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7628,31 +7642,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 58,031</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Classification of Liabilities as Current or Non-current (Amendments to IAS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F101" s="5" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -7673,12 +7683,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>financial statements.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Amounts receivable (14,219)</t>
+          <t>exercise of a conversion option meeting the definition of an equity instrument. The amendments are effective for annual periods beginning on January 1,</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -7687,13 +7697,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" s="5" t="n">
-        <v>-0.001102</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -7712,28 +7722,20 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>following working capital items</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 193,983</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>For the period of incorporation from March 9 to December 31</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.010125</v>
+        <v>0.002021</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -7759,26 +7761,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital 179,764</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Net loss for the year (439,280)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.009023</v>
+        <v>-0.115101</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7804,26 +7802,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (121,485)</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Shares issued for exploration and evaluation expenses 80,000</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>-0.038078</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7849,22 +7845,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Shares issued for exploration and evaluation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Shares subscriptions -</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Share-based payments, note 7 58,031</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.55675</v>
+        <v>0.068</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Non-brokered private placement, note 6 408,110</t>
+          <t>Amounts receivable (14,219)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.14</v>
+        <v>-0.001102</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -7931,24 +7931,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Flow-through shares, note 6 483,767</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 193,983</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="5" t="n">
+        <v>0.010125</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -7974,22 +7976,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Issue costs, note 6 (117,882)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Net change in non-cash working capital 179,764</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-0.140553</v>
+        <v>0.009023</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -8015,17 +8021,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 773,995</t>
+          <t>Net cash used in operating activities (121,485)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8034,7 +8040,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.5561970000000001</v>
+        <v>-0.038078</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -8065,21 +8071,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Change in cash 652,510</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Shares subscriptions -</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.518119</v>
+        <v>0.55675</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -8110,12 +8112,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 518,119</t>
+          <t>Non-brokered private placement, note 6 408,110</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8123,10 +8125,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="5" t="n">
+        <v>0.14</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -8157,21 +8157,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cash, end of year 1,170,629</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Flow-through shares, note 6 483,767</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>0.518119</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -8197,12 +8195,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Supplemental information,</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Finders' warrants issued, note 6 14,298</t>
+          <t>Issue costs, note 6 (117,882)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8212,7 +8210,7 @@
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.042405</v>
+        <v>-0.140553</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -8238,22 +8236,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>(b)  Basis of preparation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>April 4,</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Net cash provided by financing activities 773,995</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.5561970000000001</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -8279,20 +8281,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Future Accounting changes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>disclose  in  their  financial statements. The amendments are  effective for year ends beginning on or after January 1,</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>0.002023</v>
+          <t>Change in cash 652,510</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.518119</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -8318,20 +8326,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Future Accounting changes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>exercise of a conversion option meeting the definition of an equity instrument. The amendments are effective for annual periods beginning on January 1,</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>0.002023</v>
+          <t>Cash, beginning of year 518,119</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -8357,20 +8373,26 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Future Accounting changes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>entities  distinguish  between  accounting  policies  and  accounting  estimates.  The amendments are effective for year ends beginning on or after January 1,</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="n">
-        <v>0.002023</v>
+          <t>Cash, end of year 1,170,629</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.518119</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8396,26 +8418,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Supplemental information,</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>-0.115101</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finders' warrants issued, note 6 14,298</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.042405</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8441,26 +8459,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>(b)  Basis of preparation</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>April 4,</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8486,22 +8500,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Future Accounting changes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Items not affecting cash total</t>
+          <t>disclose  in  their  financial statements. The amendments are  effective for year ends beginning on or after January 1,</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" s="5" t="n">
-        <v>-0.047101</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -8527,26 +8539,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Future Accounting changes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>exercise of a conversion option meeting the definition of an equity instrument. The amendments are effective for annual periods beginning on January 1,</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" s="5" t="n">
-        <v>-0.001102</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -8572,26 +8578,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Future Accounting changes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>entities  distinguish  between  accounting  policies  and  accounting  estimates.  The amendments are effective for year ends beginning on or after January 1,</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" s="5" t="n">
-        <v>0.010125</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -8617,21 +8617,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.009023</v>
+        <v>-0.115101</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8662,21 +8662,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>following working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>-0.038078</v>
+        <v>0.068</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -8707,17 +8707,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Non-brokered private placement</t>
+          <t>Items not affecting cash total</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" s="5" t="n">
-        <v>0.14</v>
+        <v>-0.047101</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8748,17 +8748,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Shares subscriptions</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E127" s="5" t="n">
-        <v>0.55675</v>
+        <v>-0.001102</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8789,17 +8793,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Issue costs</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
-        <v>-0.140553</v>
+        <v>0.010125</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -8830,21 +8838,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Net change in non-cash working capital</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0.5561970000000001</v>
+        <v>0.009023</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -8875,21 +8883,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>following working capital items</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.518119</v>
+        <v>-0.038078</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -8925,18 +8933,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Non-brokered private placement</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0.14</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -8972,16 +8978,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Shares subscriptions</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" s="5" t="n">
-        <v>0.518119</v>
+        <v>0.55675</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -9012,17 +9014,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Issuance of broker warrants</t>
+          <t>Issue costs</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" s="5" t="n">
-        <v>0.042405</v>
+        <v>-0.140553</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -9053,17 +9055,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1. Nature of operations and going concern</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MINK Ventures Corporation (the "Company" or "MINK") was incorporated on March</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
-        <v>9e-06</v>
+        <v>0.5561970000000001</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9089,57 +9095,67 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, note 5 and note 8</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>0.9000629999999999</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>0.257268</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>0.166557</v>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.518119</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9147,136 +9163,152 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>0.005319</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>0.059739</v>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>0.02987</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>0.057447</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Cash, end of period</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.518119</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G137" s="5" t="n">
-        <v>0.015065</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>0.016428</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>0.015604</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Issuance of broker warrants</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" s="5" t="n">
-        <v>0.005817</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>0.007729</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>0.005857</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0.005066</v>
+        <v>0.042405</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>1. Nature of operations and going concern</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Professional fees, note 8</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>MINK Ventures Corporation (the "Company" or "MINK") was incorporated on March</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>9e-06</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G139" s="5" t="n">
-        <v>0.150879</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>0.107673</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>0.0965</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -9292,32 +9324,26 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation, note 5 and note 8</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F140" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.002704</v>
+        <v>0.9000629999999999</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.003618</v>
+        <v>0.257268</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.00184</v>
+        <v>0.166557</v>
       </c>
     </row>
     <row r="141">
@@ -9333,26 +9359,30 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 and note 8</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0.058031</v>
+        <v>0.005319</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.045732</v>
+        <v>0.059739</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0.028637</v>
+        <v>0.02987</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>0.124435</v>
+        <v>0.057447</v>
       </c>
     </row>
     <row r="142">
@@ -9368,7 +9398,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9376,20 +9406,24 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
-        <v>0.004998</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.036056</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.025629</v>
+        <v>0.015065</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.032514</v>
+        <v>0.016428</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>0.025602</v>
+        <v>0.015604</v>
       </c>
     </row>
     <row r="143">
@@ -9405,28 +9439,28 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Salaries and employee benefits, note 8</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.005817</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.007729</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.121523</v>
+        <v>0.0167</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.173243</v>
+        <v>0.005857</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0.156925</v>
+        <v>0.005066</v>
       </c>
     </row>
     <row r="144">
@@ -9442,28 +9476,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Professional fees, note 8</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0.115101</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>0.43928</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1.338034</v>
+        <v>0.150879</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.655108</v>
+        <v>0.107673</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.649976</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="145">
@@ -9474,15 +9512,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -9494,13 +9536,13 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.002344</v>
+        <v>0.002704</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.002062</v>
+        <v>0.003618</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>0.00087</v>
+        <v>0.00184</v>
       </c>
     </row>
     <row r="146">
@@ -9511,12 +9553,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Share-based payments, note 7 and note 8</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -9525,19 +9567,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" s="5" t="n">
+        <v>0.058031</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.079455</v>
+        <v>0.045732</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.12174</v>
+        <v>0.028637</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>0.056382</v>
+        <v>0.124435</v>
       </c>
     </row>
     <row r="147">
@@ -9548,33 +9588,33 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Flow-through share premium, note 6 and note 10</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.004998</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.036056</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.103681</v>
+        <v>0.025629</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>0.029473</v>
+        <v>0.032514</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>0.023343</v>
+        <v>0.025602</v>
       </c>
     </row>
     <row r="148">
@@ -9585,12 +9625,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Total other items</t>
+          <t>Salaries and employee benefits, note 8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -9605,13 +9645,13 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.18548</v>
+        <v>0.121523</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>0.153275</v>
+        <v>0.173243</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>0.080595</v>
+        <v>0.156925</v>
       </c>
     </row>
     <row r="149">
@@ -9622,35 +9662,33 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.115101</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-0.43928</v>
+        <v>0.43928</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>-1.152554</v>
+        <v>1.338034</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>-0.501833</v>
+        <v>0.655108</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>-0.569381</v>
+        <v>0.649976</v>
       </c>
     </row>
     <row r="150">
@@ -9661,29 +9699,33 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Net loss per common share</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>- basic</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.002344</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.002062</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.00087</v>
       </c>
     </row>
     <row r="151">
@@ -9694,29 +9736,33 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Net loss per common share</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>- diluted</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.079455</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.12174</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.056382</v>
       </c>
     </row>
     <row r="152">
@@ -9727,35 +9773,33 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>- basic</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Flow-through share premium, note 6 and note 10</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>5.719385</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>16.220744</v>
+        <v>0.103681</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>20.882494</v>
+        <v>0.029473</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>25.306946</v>
+        <v>0.023343</v>
       </c>
     </row>
     <row r="153">
@@ -9766,35 +9810,33 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>- diluted</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Total other items</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>5.719385</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>16.220744</v>
+        <v>0.18548</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>20.882494</v>
+        <v>0.153275</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>25.306946</v>
+        <v>0.080595</v>
       </c>
     </row>
     <row r="154">
@@ -9805,37 +9847,35 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F154" s="5" t="n">
+        <v>-0.43928</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.002344</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.152554</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-0.501833</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>-0.569381</v>
       </c>
     </row>
     <row r="155">
@@ -9846,37 +9886,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per common share</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Due diligence</t>
+          <t>- basic</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E155" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0.038277</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="156">
@@ -9887,35 +9919,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per common share</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Listing fees</t>
+          <t>- diluted</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" s="5" t="n">
-        <v>0.022243</v>
+        <v>-7e-08</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.008867</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="157">
@@ -9926,37 +9952,35 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>- basic</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="n">
-        <v>0.014043</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.180001</v>
+        <v>5.719385</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.150879</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.220744</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>20.882494</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>25.306946</v>
       </c>
     </row>
     <row r="158">
@@ -9965,35 +9989,37 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Period of incorporation from March 9 to December 31</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>- diluted</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.719385</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>16.220744</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>20.882494</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>25.306946</v>
       </c>
     </row>
     <row r="159">
@@ -10004,12 +10030,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Due diligence 38,277</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -10023,10 +10049,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" s="5" t="n">
+        <v>0.002344</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -10052,7 +10076,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, note 5 105,000</t>
+          <t>Due diligence</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -10061,10 +10085,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F160" s="5" t="n">
+        <v>0.038277</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -10095,23 +10117,15 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Investor relations 5,319</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>0.022243</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0.008867</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10142,22 +10156,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Listing fees 8,867</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.014043</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.022243</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.180001</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.150879</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10176,28 +10190,20 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Office and general 7,729</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Period of incorporation from March 9 to December 31</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.005817</v>
+        <v>0.002021</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10228,21 +10234,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Professional fees 180,001</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Due diligence 38,277</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F164" s="5" t="n">
-        <v>0.014043</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10273,7 +10277,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share-based payments, note 7 58,031</t>
+          <t>Exploration and evaluation, note 5 105,000</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -10282,8 +10286,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n">
-        <v>0.068</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -10314,7 +10320,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees 36,056</t>
+          <t>Investor relations 5,319</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10327,8 +10333,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F166" s="5" t="n">
-        <v>0.004998</v>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10359,21 +10367,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Total expenses 439,280</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Listing fees 8,867</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.115101</v>
+        <v>0.022243</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -10404,12 +10408,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year (439,280)</t>
+          <t>Office and general 7,729</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10418,7 +10422,7 @@
         </is>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.115101</v>
+        <v>0.005817</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10444,22 +10448,26 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Net loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>- basic (0.08)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Professional fees 180,001</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F169" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.014043</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -10485,12 +10493,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Net loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>- diluted (0.08)</t>
+          <t>Share-based payments, note 7 58,031</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -10500,7 +10508,7 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.068</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -10526,17 +10534,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>- basic 5,719,385</t>
+          <t>Transfer agent and filing fees 36,056</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10545,7 +10553,7 @@
         </is>
       </c>
       <c r="F171" s="5" t="n">
-        <v>1.614476</v>
+        <v>0.004998</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10571,17 +10579,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>- diluted 5,719,385</t>
+          <t>Total expenses 439,280</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10590,7 +10598,7 @@
         </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>1.614476</v>
+        <v>0.115101</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -10621,17 +10629,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Share-based payments, note 6</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year (439,280)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>-0.115101</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10657,38 +10669,251 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>Net loss per common share</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>- basic (0.08)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Net loss per common share</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>- diluted (0.08)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>- basic 5,719,385</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>1.614476</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>- diluted 5,719,385</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>1.614476</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Share-based payments, note 6</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
         <is>
           <t>Net loss and comprehensive loss for the period</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E174" s="5" t="n">
+      <c r="E179" s="5" t="n">
         <v>-0.115101</v>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
